--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +794,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,19 +820,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,15 +864,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -882,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1608,22 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3211,7 +3211,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,22 +3226,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3252,26 +3256,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3282,18 +3282,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,22 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,19 +4418,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,18 +4440,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,18 +4604,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,26 +4630,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4656,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4698,22 +4686,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4728,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4758,12 +4746,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4780,26 +4768,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4810,16 +4790,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4832,18 +4820,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4854,12 +4850,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4876,26 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4936,22 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4988,18 +4988,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5010,24 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,22 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5296,18 +5296,18 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5322,22 +5322,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5348,26 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,15 +6202,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6220,12 +6228,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,18 +6250,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6264,12 +6276,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,12 +6298,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,12 +6320,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6330,22 +6342,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6356,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,19 +6386,15 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>3</v>
@@ -6404,22 +6408,18 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6474,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6530,22 +6534,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,15 +8568,19 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8598,22 +8598,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,12 +8628,24 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F330" t="n">
         <v>2</v>
       </c>
@@ -8646,22 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8672,24 +8688,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8702,26 +8706,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8732,22 +8736,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8762,22 +8762,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,22 +8930,18 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,26 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9020,22 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9046,18 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,15 +10002,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,22 +10028,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,12 +10050,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,19 +10094,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,14 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10490,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10516,18 +10520,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10542,18 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,18 +10572,14 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
@@ -10891,11 +10891,11 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -10906,18 +10906,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -10928,14 +10932,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,18 +10954,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10976,14 +10980,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,14 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11020,22 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11046,18 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,18 +11072,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -11094,22 +11098,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11264,18 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,18 +11286,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11308,22 +11312,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11334,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11386,18 +11382,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11408,14 +11408,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11430,22 +11430,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12292,14 +12292,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -12436,14 +12436,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -12480,14 +12480,14 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12502,18 +12502,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12550,18 +12550,22 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F507" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -12572,22 +12576,18 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F508" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="509">
@@ -13060,14 +13060,22 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13078,22 +13086,22 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -13122,7 +13130,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13140,12 +13148,20 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13158,7 +13174,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13176,16 +13192,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13198,7 +13210,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13216,22 +13228,18 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
+      <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -13242,22 +13250,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D541" t="inlineStr"/>
+      <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -13500,14 +13500,14 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr"/>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="555">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13608,7 +13608,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -13644,14 +13644,14 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr"/>
       <c r="F562" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="563">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13680,14 +13680,14 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr"/>
       <c r="F564" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="565">
@@ -13842,14 +13842,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr"/>
       <c r="F573" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -14102,15 +14102,11 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14202,11 +14198,15 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14276,22 +14276,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F594" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="595">
@@ -14302,18 +14302,18 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F595" t="n">
@@ -14328,22 +14328,18 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -14354,22 +14350,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598">
@@ -14380,18 +14376,22 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
-      <c r="D598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -14402,18 +14402,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -14502,22 +14502,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14986,14 +14986,18 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr"/>
-      <c r="E627" t="inlineStr"/>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -15044,18 +15048,14 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr"/>
-      <c r="E630" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E630" t="inlineStr"/>
       <c r="F630" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="631">
@@ -15124,14 +15124,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15146,14 +15146,18 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr"/>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15164,18 +15168,14 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr"/>
-      <c r="E636" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E636" t="inlineStr"/>
       <c r="F636" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="637">
@@ -15248,14 +15248,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -15314,12 +15314,16 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr"/>
-      <c r="E643" t="inlineStr"/>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="F643" t="n">
         <v>3</v>
       </c>
@@ -15332,14 +15336,14 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -15412,7 +15416,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15430,7 +15434,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15484,14 +15488,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -15502,7 +15506,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15520,7 +15524,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15538,7 +15542,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15556,7 +15560,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -15592,7 +15596,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15682,14 +15686,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664">
@@ -15736,7 +15740,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15754,7 +15758,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15772,7 +15776,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15808,7 +15812,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15826,7 +15830,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -15970,7 +15974,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16006,14 +16010,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -16024,7 +16028,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16042,14 +16046,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -16060,7 +16064,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16078,7 +16082,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16096,14 +16100,14 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
@@ -16114,7 +16118,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16150,14 +16154,14 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr"/>
       <c r="F689" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="690">
@@ -16204,7 +16208,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16222,7 +16226,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16258,7 +16262,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16348,7 +16352,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16366,7 +16370,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16384,7 +16388,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16402,7 +16406,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16482,14 +16486,14 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr"/>
       <c r="F707" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="708">
@@ -16500,14 +16504,14 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
       <c r="D708" t="inlineStr"/>
       <c r="E708" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F708" t="n">
@@ -16540,12 +16544,20 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
-      <c r="D710" t="inlineStr"/>
-      <c r="E710" t="inlineStr"/>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F710" t="n">
         <v>3</v>
       </c>
@@ -16558,14 +16570,14 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="712">
@@ -16576,22 +16588,22 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F712" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="713">
@@ -16602,22 +16614,22 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F713" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="714">
@@ -16628,18 +16640,14 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr"/>
-      <c r="E714" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E714" t="inlineStr"/>
       <c r="F714" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715">
@@ -16650,7 +16658,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
@@ -16748,18 +16756,14 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F720" t="n">
@@ -16968,7 +16972,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17004,7 +17008,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17120,7 +17124,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17164,7 +17168,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17538,7 +17542,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -17600,7 +17604,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -17618,7 +17622,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
@@ -17636,18 +17640,14 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -17658,12 +17658,16 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr"/>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F765" t="n">
         <v>1</v>
       </c>
@@ -17676,14 +17680,14 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
       <c r="F766" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="767">
@@ -17694,14 +17698,14 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr"/>
       <c r="F767" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="768">
@@ -17712,14 +17716,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="769">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,22 +746,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -772,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -794,22 +790,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -820,15 +812,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -842,18 +838,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -864,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -890,18 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1608,18 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1634,22 +1634,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1660,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,22 +3200,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3226,26 +3230,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3293,7 +3293,7 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,22 +4096,18 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,26 +4122,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4156,18 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,19 +4304,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,18 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4352,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4374,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4418,15 +4418,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4440,22 +4444,18 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,18 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4630,22 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4656,26 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4686,24 +4698,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4716,26 +4720,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,12 +4750,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4768,18 +4772,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4790,22 +4802,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4820,26 +4832,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4850,12 +4854,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4872,26 +4876,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4906,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4936,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4988,26 +4988,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5018,16 +5010,24 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5296,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5322,22 +5322,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -6176,22 +6176,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,19 +6198,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6228,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6250,22 +6242,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6276,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6298,15 +6286,19 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6320,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6342,18 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,18 +6382,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6474,22 +6474,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,18 +6530,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,26 +7066,22 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7092,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,22 +7122,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,22 +8350,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8380,18 +8376,22 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,22 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8568,22 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,22 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,22 +8632,18 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,12 +8688,24 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8706,22 +8718,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8736,15 +8748,19 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8762,26 +8778,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8792,24 +8804,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8852,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8878,15 +8874,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,18 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8956,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9012,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9046,18 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,18 +9520,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,12 +9564,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -10002,19 +9994,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10028,18 +10016,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10050,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10072,18 +10064,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10094,15 +10090,19 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,18 +10468,14 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,18 +10490,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,18 +10516,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,14 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10880,22 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
@@ -10906,22 +10906,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -10932,18 +10928,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -10954,18 +10954,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10980,14 +10976,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -11002,14 +10998,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11024,18 +11020,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11050,18 +11046,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
@@ -11083,11 +11083,11 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -11286,22 +11290,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11312,14 +11312,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -11334,18 +11334,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11382,22 +11386,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11408,18 +11408,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11430,18 +11434,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12161,7 +12161,11 @@
           <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr"/>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>$87.1B</t>
+        </is>
+      </c>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
@@ -12179,7 +12183,11 @@
           <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr"/>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>$-49.7B</t>
+        </is>
+      </c>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="n">
@@ -12197,7 +12205,11 @@
           <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr"/>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>$72B</t>
+        </is>
+      </c>
       <c r="D489" t="inlineStr">
         <is>
           <t>$149.1B</t>
@@ -12216,7 +12228,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12234,7 +12246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12292,7 +12304,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -12310,7 +12322,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12346,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12436,14 +12448,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -12480,18 +12492,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -12502,22 +12518,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -13060,22 +13072,18 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13086,22 +13094,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13130,14 +13130,22 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13148,22 +13156,22 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13174,7 +13182,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13192,12 +13200,20 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13210,7 +13226,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13228,16 +13244,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E540" t="inlineStr"/>
       <c r="F540" t="n">
         <v>3</v>
       </c>
@@ -13536,14 +13548,14 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -13554,7 +13566,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -13590,7 +13602,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13608,7 +13620,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13626,7 +13638,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -13644,7 +13656,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -13662,7 +13674,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13680,14 +13692,14 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr"/>
       <c r="F564" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="565">
@@ -13842,7 +13854,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14076,18 +14088,14 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F586" t="n">
@@ -14102,11 +14110,15 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14198,18 +14210,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14350,22 +14362,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14502,22 +14514,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -15146,14 +15158,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F635" t="n">
@@ -15168,14 +15180,18 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr"/>
-      <c r="E636" t="inlineStr"/>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="F636" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="637">
@@ -15248,18 +15264,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -15416,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15434,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15488,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -15686,14 +15698,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -15740,7 +15752,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15758,7 +15770,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15776,7 +15788,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15812,14 +15824,14 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr"/>
       <c r="F670" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671">
@@ -15830,7 +15842,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -15974,7 +15986,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16010,14 +16022,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -16028,14 +16040,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -16046,7 +16058,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -16082,7 +16094,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16100,14 +16112,14 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -16118,7 +16130,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16154,7 +16166,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16226,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16262,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16352,7 +16364,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16370,7 +16382,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16388,7 +16400,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16406,7 +16418,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -17542,14 +17554,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="760">
@@ -17604,7 +17616,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -17622,7 +17634,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
@@ -17640,7 +17652,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
@@ -17658,18 +17670,14 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="766">
@@ -17680,12 +17688,16 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
-      <c r="E766" t="inlineStr"/>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F766" t="n">
         <v>1</v>
       </c>
@@ -17698,14 +17710,14 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr"/>
       <c r="F767" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="768">
@@ -17716,14 +17728,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="769">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,19 +816,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,22 +838,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -864,15 +860,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,22 +886,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,18 +930,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1608,18 +1608,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1634,18 +1638,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1660,22 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3185,7 +3185,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,26 +3200,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,18 +3252,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3282,22 +3278,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,19 +4418,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,18 +4440,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,18 +4604,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,26 +4630,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4656,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4698,16 +4686,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4720,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,12 +4746,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4772,26 +4768,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4802,24 +4790,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4832,18 +4812,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4854,12 +4842,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4876,26 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,26 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4936,22 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4954,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4988,18 +4980,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5010,22 +5010,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,18 +5266,18 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5292,22 +5292,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5322,26 +5322,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -5352,22 +5348,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,18 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6220,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,18 +6246,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6264,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,19 +6294,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6338,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6408,15 +6404,19 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>3</v>
@@ -6474,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6530,22 +6534,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8572,24 +8572,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8602,26 +8590,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8632,15 +8616,19 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8658,22 +8646,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8688,22 +8676,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8718,22 +8702,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,22 +8732,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8778,22 +8762,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -8804,12 +8792,24 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,22 +8930,18 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,22 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8986,26 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9046,18 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,18 +9520,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,15 +10002,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,22 +10028,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,12 +10050,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,19 +10094,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,14 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10490,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10516,18 +10520,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10542,18 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,18 +10572,14 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,18 +10880,18 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10906,14 +10906,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
@@ -10939,11 +10939,11 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -10954,18 +10954,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
@@ -10976,14 +10980,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,18 +11002,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11020,18 +11028,14 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,22 +11050,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11072,22 +11072,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11290,18 +11286,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11312,18 +11308,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11334,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11386,14 +11382,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11408,22 +11404,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11426,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -13072,16 +13072,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
         <v>3</v>
       </c>
@@ -13094,7 +13090,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13130,22 +13126,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13156,22 +13148,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13182,14 +13166,22 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13200,22 +13192,22 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -13226,7 +13218,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13244,12 +13236,20 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F540" t="n">
         <v>3</v>
       </c>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14110,18 +14110,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14210,18 +14210,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14362,22 +14362,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598">
@@ -14514,22 +14514,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -15158,18 +15158,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
@@ -15264,14 +15260,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr"/>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15500,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -15698,14 +15698,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15986,14 +15986,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16040,14 +16040,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -17554,14 +17554,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="760">
@@ -17616,14 +17616,14 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="763">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
@@ -17670,7 +17670,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
@@ -17688,18 +17688,14 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
-      <c r="E766" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E766" t="inlineStr"/>
       <c r="F766" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="767">
@@ -17710,12 +17706,16 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F767" t="n">
         <v>1</v>
       </c>
@@ -17728,14 +17728,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="769">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,22 +794,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -816,15 +816,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,18 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1608,22 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3174,22 +3174,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,7 +3256,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3263,7 +3267,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3278,26 +3282,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4096,22 +4096,18 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,22 +4122,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4156,18 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,19 +4304,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,18 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4352,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4374,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4418,15 +4418,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4440,22 +4444,18 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,18 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4630,22 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4656,26 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4686,22 +4698,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4716,26 +4728,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,12 +4758,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4768,18 +4780,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4790,16 +4810,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4812,26 +4840,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4842,12 +4862,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4864,26 +4884,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4894,26 +4914,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4944,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,18 +4970,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4980,26 +4996,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5010,24 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,22 +5266,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5292,26 +5296,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5322,18 +5322,18 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5348,22 +5348,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -6176,15 +6176,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6198,22 +6202,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,22 +6246,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6272,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6294,18 +6290,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,18 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,19 +6408,15 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>3</v>
@@ -6474,22 +6474,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,18 +6530,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,26 +7066,22 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7092,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,22 +7122,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,22 +8350,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8380,18 +8376,22 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,12 +8572,24 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8590,22 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8616,22 +8632,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8646,22 +8662,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8676,15 +8692,19 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8702,26 +8722,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8732,24 +8748,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8762,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8792,22 +8796,18 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8852,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8878,15 +8874,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,18 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8956,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8986,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9046,18 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -10002,19 +9994,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10028,18 +10016,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10050,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10072,18 +10064,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10094,15 +10090,19 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,18 +10468,14 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,18 +10490,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,18 +10516,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,14 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,18 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10906,14 +10902,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,22 +10924,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10954,22 +10950,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10980,18 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -11002,7 +10998,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
@@ -11013,11 +11009,11 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -11028,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,18 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,18 +11290,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -11308,22 +11316,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11334,14 +11338,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F449" t="n">
@@ -11382,18 +11386,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11404,18 +11412,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11426,22 +11434,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -13072,12 +13072,20 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F532" t="n">
         <v>3</v>
       </c>
@@ -13090,7 +13098,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13126,16 +13134,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
         <v>3</v>
       </c>
@@ -13148,7 +13152,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13166,22 +13170,18 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13192,22 +13192,14 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -13218,14 +13210,22 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F539" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -13236,22 +13236,22 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14110,18 +14110,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14210,18 +14210,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14362,22 +14362,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14514,22 +14514,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -15158,14 +15158,18 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr"/>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15260,18 +15264,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15500,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -15698,14 +15698,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15824,14 +15824,14 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr"/>
       <c r="F670" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="671">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16130,14 +16130,14 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -17554,14 +17554,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="760">
@@ -17616,14 +17616,18 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
-      <c r="E762" t="inlineStr"/>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F762" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="763">
@@ -17634,14 +17638,14 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764">
@@ -17652,7 +17656,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
@@ -17670,7 +17674,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
@@ -17688,7 +17692,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
@@ -17706,18 +17710,14 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E767" t="inlineStr"/>
       <c r="F767" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="768">
@@ -17728,12 +17728,16 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
-      <c r="E768" t="inlineStr"/>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F768" t="n">
         <v>1</v>
       </c>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +794,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,19 +820,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,15 +864,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -882,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1608,22 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,22 +3200,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3226,26 +3230,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3293,7 +3293,7 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,22 +4126,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,19 +4418,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,18 +4440,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,18 +4604,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,26 +4630,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4656,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4698,22 +4686,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4728,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4758,12 +4746,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4780,26 +4768,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4810,16 +4790,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4832,18 +4820,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4854,12 +4850,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4876,26 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4936,22 +4932,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4988,18 +4988,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5010,24 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,18 +5266,18 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5292,22 +5292,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5322,26 +5322,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -5352,22 +5348,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -6176,22 +6176,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,19 +6198,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6228,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6250,18 +6242,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6272,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6294,15 +6290,19 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,22 +6338,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,18 +6382,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6474,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6530,22 +6534,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,22 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8568,22 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,22 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,22 +8632,18 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8688,12 +8688,24 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8706,22 +8718,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8736,15 +8748,19 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8762,26 +8778,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8792,24 +8804,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,22 +8930,18 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,26 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9020,22 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9046,18 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,15 +10002,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,22 +10028,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,12 +10050,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,19 +10094,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,14 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10490,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10516,18 +10520,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10542,18 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,18 +10572,14 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
@@ -10913,11 +10913,11 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -10928,18 +10928,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -10950,14 +10954,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10972,18 +10976,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,18 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11024,14 +11024,14 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,18 +11046,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11068,22 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11094,22 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,22 +11290,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11312,22 +11312,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11338,18 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11386,18 +11382,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -11408,18 +11408,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11430,14 +11434,14 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13090,16 +13090,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr"/>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
         <v>3</v>
       </c>
@@ -13130,22 +13126,14 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13156,22 +13144,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13182,22 +13166,22 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13208,14 +13192,22 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -13226,12 +13218,20 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14110,18 +14110,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14210,18 +14210,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14362,22 +14362,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598">
@@ -14514,22 +14514,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -15158,18 +15158,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
@@ -15264,14 +15260,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr"/>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15500,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -15698,14 +15698,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16022,14 +16022,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16058,14 +16058,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16112,14 +16112,14 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr"/>
       <c r="F686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -16130,7 +16130,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16166,14 +16166,14 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr"/>
       <c r="F689" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="690">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -17616,18 +17616,18 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F762" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="763">
@@ -17638,12 +17638,16 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
-      <c r="E763" t="inlineStr"/>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F763" t="n">
         <v>1</v>
       </c>
@@ -17656,18 +17660,14 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="765">
@@ -17678,14 +17678,18 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr"/>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F765" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="766">
@@ -17696,14 +17700,14 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
       <c r="F766" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="767">
@@ -17714,7 +17718,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
@@ -17732,7 +17736,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,22 +746,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -772,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -794,22 +790,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -820,15 +812,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -842,18 +838,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -864,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -890,18 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1608,18 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1634,22 +1634,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1660,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3185,7 +3185,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,26 +3200,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,18 +3252,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3282,22 +3278,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,22 +4096,18 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,26 +4122,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4156,18 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,19 +4304,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,18 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4352,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4374,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4418,15 +4418,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4440,22 +4444,18 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,18 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4630,22 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4656,26 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4686,24 +4698,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4716,26 +4720,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,12 +4750,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4768,18 +4772,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4790,22 +4802,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4820,26 +4832,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4850,12 +4854,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4872,26 +4876,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4902,26 +4906,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4932,26 +4936,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4988,26 +4988,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5018,16 +5010,24 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,22 +5266,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5292,26 +5296,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5322,18 +5322,18 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5348,22 +5348,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,18 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6220,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,22 +6246,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,19 +6290,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6316,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,18 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6408,15 +6404,19 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>3</v>
@@ -6474,22 +6474,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,18 +6530,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,26 +7066,22 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7092,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,22 +7122,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,22 +8350,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8380,18 +8376,22 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8572,24 +8572,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8602,26 +8590,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8632,15 +8616,19 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8658,22 +8646,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8688,22 +8676,18 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8718,22 +8702,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,22 +8732,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8778,22 +8762,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -8804,12 +8792,24 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F336" t="n">
         <v>2</v>
       </c>
@@ -8852,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8878,15 +8874,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,18 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8956,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9012,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9046,18 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,18 +9520,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,12 +9564,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -10002,19 +9994,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10028,18 +10016,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10050,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10072,18 +10064,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10094,15 +10090,19 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,18 +10468,14 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,18 +10490,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,18 +10516,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,14 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,22 +10902,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -10928,22 +10928,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10954,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
@@ -10976,18 +10976,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -11002,18 +10998,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11024,14 +11024,14 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
@@ -11057,11 +11057,11 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -11072,14 +11072,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11094,18 +11094,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11290,14 +11286,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -11312,18 +11308,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11334,18 +11334,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -11382,22 +11386,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11408,22 +11408,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11430,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13090,12 +13090,20 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr"/>
-      <c r="E533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F533" t="n">
         <v>3</v>
       </c>
@@ -13126,7 +13134,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13144,16 +13152,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13166,22 +13170,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13192,22 +13188,18 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -13218,22 +13210,22 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F539" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -13244,14 +13236,22 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14110,18 +14110,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14210,18 +14210,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14362,22 +14362,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14514,22 +14514,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -15158,14 +15158,18 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr"/>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15260,18 +15264,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15500,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -15698,14 +15698,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15824,14 +15824,14 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr"/>
       <c r="F670" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16022,14 +16022,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16058,14 +16058,14 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -16094,14 +16094,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -17616,16 +17616,12 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
-      <c r="E762" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
         <v>2</v>
       </c>
@@ -17638,18 +17634,18 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F763" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="764">
@@ -17660,12 +17656,16 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr"/>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F764" t="n">
         <v>1</v>
       </c>
@@ -17678,18 +17678,14 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="766">
@@ -17700,14 +17696,18 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
-      <c r="E766" t="inlineStr"/>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F766" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="767">
@@ -17718,14 +17718,14 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr"/>
       <c r="F767" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="768">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,19 +816,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,22 +838,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -864,15 +860,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,22 +886,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,18 +930,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1608,18 +1608,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1634,18 +1638,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1660,22 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,22 +3174,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,7 +3256,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3263,7 +3267,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3278,26 +3282,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,22 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,19 +4418,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,18 +4440,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,18 +4604,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,26 +4630,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4656,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4698,16 +4686,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4720,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,12 +4746,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4772,26 +4768,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4802,24 +4790,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4832,18 +4812,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4854,12 +4842,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4876,26 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,26 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4936,22 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4954,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4988,18 +4980,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5010,22 +5010,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,22 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5296,18 +5296,18 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5322,22 +5322,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -5348,26 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -6176,15 +6176,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6198,22 +6202,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,18 +6246,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,18 +6294,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6312,12 +6320,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6342,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,19 +6408,15 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>3</v>
@@ -6474,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6530,22 +6534,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,12 +8572,24 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8590,22 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8616,22 +8632,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8646,22 +8662,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8676,15 +8692,19 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8702,26 +8722,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8732,24 +8748,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8762,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8792,22 +8796,18 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,22 +8930,18 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,22 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8986,26 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9046,18 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,18 +9520,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,15 +10002,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,22 +10028,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,12 +10050,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,19 +10094,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,14 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10490,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10516,18 +10520,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10542,18 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,18 +10572,14 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,18 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,14 +10928,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
@@ -10961,11 +10961,11 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -10976,18 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,18 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -11046,22 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11072,14 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11094,18 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11264,18 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,18 +11286,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11308,22 +11312,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11334,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11386,18 +11382,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11408,14 +11408,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11430,22 +11430,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -13072,14 +13072,22 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13090,22 +13098,22 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -13134,7 +13142,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13152,12 +13160,20 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13170,7 +13186,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13188,16 +13204,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13210,22 +13222,14 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
@@ -13236,22 +13240,18 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14110,18 +14110,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14210,18 +14210,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14362,22 +14362,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598">
@@ -14514,22 +14514,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -15158,18 +15158,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
@@ -15264,14 +15260,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr"/>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15500,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -15698,14 +15698,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15824,14 +15824,14 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr"/>
       <c r="F670" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="671">
@@ -15986,14 +15986,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -16076,14 +16076,14 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
       <c r="F684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
@@ -16094,14 +16094,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -17616,7 +17616,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -17634,16 +17634,12 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
-      <c r="E763" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
         <v>2</v>
       </c>
@@ -17656,18 +17652,18 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F764" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -17678,12 +17674,16 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr"/>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F765" t="n">
         <v>1</v>
       </c>
@@ -17696,18 +17696,14 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
-      <c r="E766" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="E766" t="inlineStr"/>
       <c r="F766" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="767">
@@ -17718,14 +17714,18 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F767" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="768">
@@ -17736,14 +17736,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="769">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,22 +794,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -816,15 +816,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,19 +864,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,18 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1608,22 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3174,26 +3174,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3204,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3230,7 +3226,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3241,7 +3237,7 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,22 +3252,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3282,18 +3282,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4096,22 +4096,18 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,22 +4122,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4156,18 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,18 +4278,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4300,19 +4304,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,18 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4352,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,12 +4374,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4418,15 +4418,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4440,22 +4444,18 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,18 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4604,18 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4630,22 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4656,26 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4686,22 +4698,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4716,26 +4728,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,12 +4758,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4768,18 +4780,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4790,16 +4810,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4812,26 +4840,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4842,12 +4862,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4864,26 +4884,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4894,26 +4914,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4944,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,18 +4970,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4980,26 +4996,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5010,24 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5296,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5322,22 +5322,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -6176,19 +6176,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6202,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6224,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,22 +6242,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6272,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6294,22 +6286,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6320,12 +6308,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6342,18 +6330,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,15 +6378,19 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>3</v>
@@ -6408,18 +6404,22 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -6474,22 +6474,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,18 +6530,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,26 +7066,22 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7092,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,22 +7122,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,22 +8350,18 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8380,18 +8376,22 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,22 +8572,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8602,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8632,24 +8628,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="n">
         <v>2</v>
       </c>
@@ -8662,26 +8646,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8692,22 +8672,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8722,22 +8702,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -8748,12 +8732,24 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,22 +8762,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8796,15 +8792,19 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8852,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8878,15 +8874,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,18 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8956,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8986,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9046,18 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -10002,19 +9994,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10028,18 +10016,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10050,12 +10042,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10072,18 +10064,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10094,15 +10090,19 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,18 +10468,14 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,18 +10490,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,18 +10516,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,14 +10568,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
@@ -10880,18 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -10902,18 +10906,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,14 +10928,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,22 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10976,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -11002,14 +10998,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11024,7 +11020,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
@@ -11035,11 +11031,11 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11046,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11076,14 +11072,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,18 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -11286,22 +11290,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11312,14 +11312,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -11334,18 +11334,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11382,22 +11386,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11408,18 +11408,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11430,18 +11434,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -13072,22 +13072,18 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13098,22 +13094,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13142,14 +13130,22 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13160,22 +13156,22 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13186,7 +13182,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13204,12 +13200,20 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13222,7 +13226,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13240,16 +13244,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E540" t="inlineStr"/>
       <c r="F540" t="n">
         <v>3</v>
       </c>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14110,18 +14110,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14210,18 +14210,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14362,22 +14362,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14514,22 +14514,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -15158,14 +15158,18 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr"/>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15260,18 +15264,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15500,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -15698,14 +15698,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15986,14 +15986,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16130,14 +16130,14 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -17554,14 +17554,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="760">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
@@ -17652,16 +17652,12 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
         <v>2</v>
       </c>
@@ -17674,18 +17670,18 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
       <c r="E765" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F765" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="766">
@@ -17696,12 +17692,16 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
-      <c r="E766" t="inlineStr"/>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F766" t="n">
         <v>1</v>
       </c>
@@ -17714,18 +17714,14 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="E767" t="inlineStr"/>
       <c r="F767" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="768">
@@ -17736,14 +17732,18 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
-      <c r="E768" t="inlineStr"/>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F768" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="769">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,22 +746,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -772,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -794,18 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -816,19 +816,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -842,18 +838,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -864,15 +864,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -886,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -912,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1608,18 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1634,22 +1634,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1660,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3211,7 +3211,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,22 +3226,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3252,26 +3256,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3282,18 +3282,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,26 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4096,18 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>-12.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4152,22 +4156,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4278,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4304,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,22 +4326,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,19 +4418,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4444,18 +4440,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,18 +4604,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4638,26 +4630,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4656,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4698,24 +4686,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4728,26 +4708,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4758,12 +4738,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4780,26 +4760,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4810,22 +4782,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4840,18 +4812,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4862,12 +4842,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4884,26 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4914,26 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4944,22 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4970,18 +4954,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4996,18 +4980,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5018,16 +5010,24 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -5266,18 +5266,18 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5292,22 +5292,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -5322,26 +5322,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -5352,22 +5348,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.148M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,15 +6202,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6220,12 +6228,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,18 +6250,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6264,12 +6276,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,12 +6298,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,12 +6320,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6330,22 +6342,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6356,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,19 +6386,15 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>3</v>
@@ -6404,22 +6408,18 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6474,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6530,22 +6534,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7066,22 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -7092,26 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7480,18 +7480,18 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>$-105.4B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,26 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,15 +8568,19 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8598,22 +8598,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,12 +8628,24 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F330" t="n">
         <v>2</v>
       </c>
@@ -8646,22 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8672,24 +8688,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="n">
         <v>2</v>
       </c>
@@ -8702,26 +8706,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8732,22 +8736,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8762,22 +8762,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,22 +8930,18 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8956,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8982,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9046,18 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,18 +9520,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,12 +9564,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,15 +10002,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,22 +10028,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,12 +10050,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,19 +10094,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10468,14 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>317.42</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10490,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10516,18 +10520,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10542,18 +10546,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,18 +10572,14 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>317.42</t>
-        </is>
-      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F412" t="n">
@@ -10594,18 +10594,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
@@ -10891,11 +10891,11 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -10906,18 +10906,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -10928,14 +10932,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,18 +10954,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10976,14 +10980,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,14 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11020,22 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11046,18 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,18 +11072,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -11094,22 +11098,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11264,22 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11290,18 +11286,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11312,18 +11308,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11334,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11386,14 +11382,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11408,22 +11404,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11426,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -13072,16 +13072,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
         <v>3</v>
       </c>
@@ -13094,7 +13090,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13130,22 +13126,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13156,22 +13148,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13182,14 +13166,22 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13200,22 +13192,22 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -13226,7 +13218,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13244,12 +13236,20 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F540" t="n">
         <v>3</v>
       </c>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -14110,18 +14110,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14210,18 +14210,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14362,22 +14362,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598">
@@ -14514,22 +14514,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.12M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -15158,18 +15158,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
+      <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636">
@@ -15264,14 +15260,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr"/>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15500,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -15698,14 +15698,14 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr"/>
       <c r="F663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16040,14 +16040,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -16076,14 +16076,14 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
       <c r="F684" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
@@ -16094,14 +16094,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16130,14 +16130,14 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -17554,14 +17554,18 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
-      <c r="E759" t="inlineStr"/>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F759" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="760">
@@ -17616,14 +17620,14 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="763">
@@ -17634,7 +17638,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
@@ -17652,7 +17656,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
@@ -17670,16 +17674,12 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
         <v>2</v>
       </c>
@@ -17692,18 +17692,18 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F766" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="767">
@@ -17714,12 +17714,16 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F767" t="n">
         <v>1</v>
       </c>
@@ -17732,18 +17736,14 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
-      <c r="E768" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="769">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +794,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,19 +820,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,15 +864,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -882,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1608,22 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2198,22 +2198,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2228,22 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,15 +2354,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>3</v>
@@ -2376,18 +2380,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,12 +2406,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2420,18 +2428,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2442,22 +2454,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2468,19 +2476,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
@@ -2494,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2516,22 +2520,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/09</t>
+          <t>15-Year Mortgage RateJAN/09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/09</t>
+          <t>30-Year Mortgage RateJAN/09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,22 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,10 +3330,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3626,10 +3626,14 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,22 +3648,18 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,26 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,18 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,26 +3734,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,18 +3970,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,22 +4300,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4348,22 +4348,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,22 +4440,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4604,22 +4604,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4634,26 +4634,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4664,18 +4660,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4690,26 +4686,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -4720,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,12 +4746,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4772,26 +4768,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4802,26 +4790,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4832,18 +4812,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4854,12 +4842,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4876,26 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,18 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4928,26 +4924,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4958,22 +4950,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,18 +4980,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5010,26 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5784,18 +5784,18 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -5828,18 +5828,18 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -5968,22 +5968,18 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -5998,26 +5994,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6028,22 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,18 +6202,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6220,12 +6228,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,15 +6294,19 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6308,22 +6320,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6334,22 +6342,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6404,19 +6408,15 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>3</v>
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6620,12 +6616,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6650,26 +6646,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7342,26 +7342,26 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,18 +7372,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7398,22 +7398,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7424,22 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,18 +7642,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -7664,18 +7664,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7816,22 +7816,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7842,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,19 +7908,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8000,22 +8000,22 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -8096,22 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8126,26 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8156,18 +8156,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,22 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8208,26 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8238,18 +8238,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8264,26 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/30</t>
+          <t>15-Year Mortgage RateJAN/30</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>6.12%</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/30</t>
+          <t>30-Year Mortgage RateJAN/30</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8990,18 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9042,26 +9046,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,15 +10002,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,22 +10028,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,12 +10050,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,19 +10094,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,14 +10414,14 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="406">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,14 +10450,14 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,18 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -10902,14 +10906,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,7 +10928,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
@@ -10935,11 +10939,11 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -10950,14 +10954,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10972,18 +10980,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,22 +11002,18 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,14 +11024,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,18 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,22 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11098,18 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/13</t>
+          <t>30-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/13</t>
+          <t>15-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -11478,14 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F455" t="n">
@@ -11500,22 +11504,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F456" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="457">
@@ -11526,22 +11526,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -11552,14 +11552,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11574,18 +11574,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F459" t="n">
@@ -11763,11 +11763,7 @@
           <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
+      <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
           <t>-1</t>
@@ -11793,7 +11789,11 @@
           <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
       <c r="D469" t="inlineStr">
         <is>
           <t>-1</t>
@@ -12006,14 +12006,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr"/>
+          <t>42-Day Bill Auction</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>4.270%</t>
+        </is>
+      </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12027,7 +12031,11 @@
           <t>52-Week Bill Auction</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr"/>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
@@ -12042,18 +12050,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -12064,14 +12068,10 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>4.270%</t>
-        </is>
-      </c>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -12322,14 +12322,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -12394,18 +12394,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -12416,18 +12420,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12560,22 +12564,18 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
@@ -13036,20 +13036,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D530" t="inlineStr"/>
+      <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
         <v>3</v>
       </c>
@@ -13062,12 +13054,20 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F531" t="n">
         <v>3</v>
       </c>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13098,16 +13098,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr"/>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
         <v>3</v>
       </c>
@@ -13120,12 +13116,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F534" t="n">
         <v>3</v>
       </c>
@@ -13138,22 +13138,14 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13164,18 +13156,18 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F536" t="n">
@@ -13190,14 +13182,22 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
@@ -13476,14 +13476,14 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="553">
@@ -13494,14 +13494,14 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr"/>
       <c r="F553" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -13512,14 +13512,14 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr"/>
       <c r="F554" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13620,14 +13620,14 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr"/>
       <c r="F560" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="561">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -14090,18 +14090,18 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F585" t="n">
@@ -14116,11 +14116,15 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E586" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14138,18 +14142,14 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14368,22 +14368,18 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -14394,18 +14390,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14416,18 +14416,18 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F598" t="n">
@@ -14442,18 +14442,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -14468,22 +14468,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14494,22 +14494,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
@@ -14878,12 +14878,16 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr"/>
-      <c r="E621" t="inlineStr"/>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F621" t="n">
         <v>3</v>
       </c>
@@ -14896,18 +14900,18 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr"/>
       <c r="E622" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="F622" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="623">
@@ -14918,16 +14922,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr"/>
-      <c r="E623" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E623" t="inlineStr"/>
       <c r="F623" t="n">
         <v>3</v>
       </c>
@@ -14940,18 +14940,18 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr"/>
       <c r="E624" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F624" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="625">
@@ -15064,14 +15064,14 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F630" t="n">
@@ -15144,14 +15144,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15188,14 +15188,14 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F636" t="n">
@@ -15276,14 +15276,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -15298,14 +15298,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15356,7 +15356,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15500,14 +15500,14 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr"/>
       <c r="E652" t="inlineStr"/>
       <c r="F652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -15608,14 +15608,14 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr"/>
       <c r="E658" t="inlineStr"/>
       <c r="F658" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="659">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -15932,7 +15932,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -15968,7 +15968,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16022,14 +16022,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -16040,14 +16040,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -16076,14 +16076,14 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr"/>
       <c r="F684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
@@ -16094,14 +16094,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16638,14 +16638,18 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr"/>
-      <c r="E713" t="inlineStr"/>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F713" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="714">
@@ -16656,18 +16660,14 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr"/>
-      <c r="E714" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E714" t="inlineStr"/>
       <c r="F714" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="715">
@@ -16678,18 +16678,18 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F715" t="n">
@@ -16704,14 +16704,22 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="717">
@@ -16722,14 +16730,14 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
       <c r="F717" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="718">
@@ -16740,14 +16748,14 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr"/>
       <c r="F718" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="719">
@@ -16758,12 +16766,16 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
-      <c r="E719" t="inlineStr"/>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F719" t="n">
         <v>3</v>
       </c>
@@ -16776,18 +16788,22 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F720" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="721">
@@ -16798,22 +16814,22 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F721" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="722">
@@ -16824,14 +16840,14 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
       <c r="F722" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="723">
@@ -16842,22 +16858,14 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" t="inlineStr"/>
       <c r="F723" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="724">
@@ -16868,20 +16876,12 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
-      <c r="D724" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E724" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D724" t="inlineStr"/>
+      <c r="E724" t="inlineStr"/>
       <c r="F724" t="n">
         <v>3</v>
       </c>
@@ -16894,14 +16894,14 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr"/>
       <c r="F725" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="726">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -16966,7 +16966,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17332,18 +17332,14 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
-      <c r="E748" t="inlineStr">
-        <is>
-          <t>2.7%</t>
-        </is>
-      </c>
+      <c r="E748" t="inlineStr"/>
       <c r="F748" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749">
@@ -17504,14 +17500,14 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr"/>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="757">
@@ -17522,14 +17518,18 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr"/>
-      <c r="E757" t="inlineStr"/>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F757" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="758">
@@ -17540,14 +17540,14 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr"/>
       <c r="E758" t="inlineStr"/>
       <c r="F758" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="759">
@@ -17558,18 +17558,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
-      <c r="E759" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="760">
@@ -17642,14 +17638,18 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
-      <c r="E763" t="inlineStr"/>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F763" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764">
@@ -17660,14 +17660,14 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="765">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-01.xlsx
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +772,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +794,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,19 +820,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.323M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,12 +842,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,15 +864,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -882,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1608,22 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$351.6B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$273.4B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1664,18 +1664,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$351.6B</t>
+          <t>$273.4B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2198,22 +2198,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2228,22 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,15 +2354,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>3</v>
@@ -2376,18 +2380,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,12 +2406,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2420,18 +2428,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2442,22 +2454,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2468,19 +2476,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
@@ -2494,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2516,22 +2520,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/09</t>
+          <t>15-Year Mortgage RateJAN/09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/09</t>
+          <t>30-Year Mortgage RateJAN/09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,14 +3308,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3330,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3352,12 +3348,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3374,10 +3370,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3558,26 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,26 +3584,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,22 +3614,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,18 +3640,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,26 +3670,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,12 +3700,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,11 +3715,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3734,7 +3730,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3742,10 +3738,14 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,18 +3970,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,22 +4300,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>1.1M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4348,22 +4348,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4374,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,22 +4440,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -4604,18 +4604,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4630,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4660,26 +4660,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4690,22 +4682,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4720,26 +4712,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4750,12 +4742,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4772,26 +4764,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4802,26 +4786,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4832,18 +4812,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4854,12 +4842,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4876,26 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,18 +4894,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -4932,26 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,18 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,22 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5740,18 +5740,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5784,12 +5784,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5806,12 +5806,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -5828,18 +5828,18 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -5968,22 +5968,18 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -5998,26 +5994,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6028,22 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,19 +6202,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,22 +6246,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6272,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6294,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,22 +6338,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6364,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6386,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6408,15 +6404,19 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
         <v>3</v>
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6616,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6646,12 +6650,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7342,18 +7342,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,26 +7368,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -7398,22 +7398,18 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,22 +7424,26 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,18 +7642,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,22 +7864,18 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -7890,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7912,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7934,18 +7930,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,18 +7956,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7982,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8000,19 +8004,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>3</v>
@@ -8096,22 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8126,26 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F311" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8156,18 +8156,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,26 +8182,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,18 +8208,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,18 +8234,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8264,26 +8260,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8290,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,22 +8320,26 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/30</t>
+          <t>15-Year Mortgage RateJAN/30</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>6.12%</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/30</t>
+          <t>30-Year Mortgage RateJAN/30</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8990,18 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,22 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9042,26 +9046,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -9734,22 +9734,22 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalJAN</t>
+          <t>S&amp;P Global Services PMI FinalJAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F375" t="n">
@@ -9764,22 +9764,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalJAN</t>
+          <t>S&amp;P Global Composite PMI FinalJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,18 +9976,22 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -9994,15 +10002,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10016,22 +10028,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10042,12 +10050,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10064,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,19 +10094,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,14 +10450,14 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,18 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -10902,14 +10906,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,7 +10928,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
@@ -10935,11 +10939,11 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -10950,14 +10954,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10972,18 +10980,14 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -10998,22 +11002,18 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,14 +11024,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,18 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,22 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11098,18 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/13</t>
+          <t>30-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/13</t>
+          <t>15-Year Mortgage RateFEB/13</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -11478,18 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F455" t="n">
@@ -11504,14 +11504,14 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11526,22 +11526,18 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
@@ -11552,14 +11548,18 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11574,22 +11574,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -11763,11 +11763,7 @@
           <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
+      <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
           <t>-1</t>
@@ -11793,7 +11789,11 @@
           <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
       <c r="D469" t="inlineStr">
         <is>
           <t>-1</t>
@@ -12009,7 +12009,11 @@
           <t>52-Week Bill Auction</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr"/>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="n">
@@ -12024,14 +12028,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr"/>
+          <t>42-Day Bill Auction</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>4.270%</t>
+        </is>
+      </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12042,14 +12050,10 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>4.270%</t>
-        </is>
-      </c>
+          <t>52-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
@@ -12064,18 +12068,14 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
+          <t>Fed Barr Speech</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12360,14 +12360,14 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12378,14 +12378,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -12414,22 +12414,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12440,18 +12436,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501">
@@ -12596,18 +12596,18 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F506" t="n">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -13098,16 +13098,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
         <v>3</v>
       </c>
@@ -13120,12 +13116,16 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F532" t="n">
         <v>3</v>
       </c>
@@ -13138,22 +13138,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13164,18 +13156,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F534" t="n">
@@ -13190,14 +13182,22 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13208,20 +13208,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13234,12 +13226,20 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F537" t="n">
         <v>3</v>
       </c>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
@@ -14134,18 +14134,18 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F585" t="n">
@@ -14160,11 +14160,15 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E586" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14182,18 +14186,14 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14412,22 +14412,18 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -14438,18 +14434,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -14460,18 +14460,18 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F598" t="n">
@@ -14486,18 +14486,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -14512,22 +14512,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14538,22 +14538,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -15344,14 +15344,14 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr"/>
       <c r="E640" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -15366,14 +15366,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -15568,7 +15568,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -16066,14 +16066,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16102,14 +16102,14 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -16120,14 +16120,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -16174,14 +16174,14 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16446,12 +16446,16 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
-      <c r="E699" t="inlineStr"/>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F699" t="n">
         <v>3</v>
       </c>
@@ -16762,14 +16766,14 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="714">
@@ -16780,14 +16784,14 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715">
@@ -16798,20 +16802,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
-      <c r="D715" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D715" t="inlineStr"/>
+      <c r="E715" t="inlineStr"/>
       <c r="F715" t="n">
         <v>3</v>
       </c>
@@ -16824,14 +16820,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
@@ -16842,14 +16838,22 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F717" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="718">
@@ -16860,18 +16864,14 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr"/>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E718" t="inlineStr"/>
       <c r="F718" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="719">
@@ -16882,18 +16882,22 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F719" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -16904,22 +16908,22 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F720" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="721">
@@ -16930,18 +16934,18 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F721" t="n">
@@ -16956,22 +16960,14 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D722" t="inlineStr"/>
+      <c r="E722" t="inlineStr"/>
       <c r="F722" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="723">
@@ -16982,14 +16978,14 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr"/>
       <c r="F723" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="724">
@@ -17000,12 +16996,16 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr"/>
-      <c r="E724" t="inlineStr"/>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F724" t="n">
         <v>3</v>
       </c>
@@ -17018,14 +17018,18 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr"/>
-      <c r="E725" t="inlineStr"/>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F725" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="726">
@@ -17080,7 +17084,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -17098,7 +17102,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
@@ -17640,7 +17644,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
@@ -17680,14 +17684,14 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr"/>
       <c r="E758" t="inlineStr"/>
       <c r="F758" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="759">
@@ -17698,18 +17702,14 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
-      <c r="E759" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E759" t="inlineStr"/>
       <c r="F759" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="760">
@@ -17782,14 +17782,18 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
-      <c r="E763" t="inlineStr"/>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F763" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764">
@@ -17800,14 +17804,14 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="765">
